--- a/Excel/Excel Workbook/VLOOKUP Example.xlsx
+++ b/Excel/Excel Workbook/VLOOKUP Example.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\My Projects\Data Projects\My Data Science Full Kit\Complete_Data_Science_Full_Course\Excel\Excel Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90CD5A62-4B34-481C-8A04-12DFBFEF5D5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CEEB28D-CC9D-421D-AF15-E9F100F538DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,30 +32,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="41">
   <si>
     <t xml:space="preserve">    Name</t>
   </si>
@@ -178,9 +156,6 @@
   </si>
   <si>
     <t>Name</t>
-  </si>
-  <si>
-    <t>Cloyster</t>
   </si>
 </sst>
 </file>
@@ -550,10 +525,6 @@
         <f>VLOOKUP(G2,A2:B21,2,FALSE)</f>
         <v>Water</v>
       </c>
-      <c r="J2">
-        <f>VLOOKUP(G2,A2:D21,4,FALSE)</f>
-        <v>525</v>
-      </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
@@ -567,13 +538,6 @@
       </c>
       <c r="D3">
         <v>510</v>
-      </c>
-      <c r="G3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H3" t="e" cm="1">
-        <f t="array" aca="1" ref="H3" ca="1">XLOOPUP(G3,A2:A21,B2:B21)</f>
-        <v>#NAME?</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
